--- a/aec/results/강남/linear_results.xlsx
+++ b/aec/results/강남/linear_results.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="단변량_univariate" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다변량_coefficients" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다변량_model_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="단변량_univariate" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="다변량_coefficients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="다변량_model_summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/aec/results/강남/linear_results.xlsx
+++ b/aec/results/강남/linear_results.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="단변량_univariate" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="다변량_coefficients" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="다변량_model_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="단변량_univariate" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다변량_coefficients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다변량_model_summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -484,28 +484,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44.6571</v>
+        <v>44.8363</v>
       </c>
       <c r="C2" t="n">
-        <v>42.5833</v>
+        <v>42.7614</v>
       </c>
       <c r="D2" t="n">
-        <v>46.7309</v>
+        <v>46.9113</v>
       </c>
       <c r="E2" t="n">
-        <v>1.0574</v>
+        <v>1.0579</v>
       </c>
       <c r="F2" t="n">
-        <v>42.2349</v>
+        <v>42.3824</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5068</v>
+        <v>0.5181</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5065</v>
+        <v>0.5178</v>
       </c>
     </row>
     <row r="3">
@@ -515,28 +515,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-2.684</v>
+        <v>-2.993</v>
       </c>
       <c r="C3" t="n">
-        <v>-4.1192</v>
+        <v>-4.4487</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.2488</v>
+        <v>-1.5374</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7317</v>
+        <v>0.7422</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.668</v>
+        <v>-4.0329</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000252</v>
+        <v>5.8e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0077</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0071</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -546,28 +546,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.1426</v>
+        <v>11.171</v>
       </c>
       <c r="C4" t="n">
-        <v>9.800700000000001</v>
+        <v>9.81</v>
       </c>
       <c r="D4" t="n">
-        <v>12.4844</v>
+        <v>12.5319</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6842</v>
+        <v>0.6939</v>
       </c>
       <c r="F4" t="n">
-        <v>16.2864</v>
+        <v>16.0993</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1325</v>
+        <v>0.1343</v>
       </c>
       <c r="I4" t="n">
-        <v>0.132</v>
+        <v>0.1338</v>
       </c>
     </row>
     <row r="5">
@@ -577,28 +577,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-10.7427</v>
+        <v>-10.6401</v>
       </c>
       <c r="C5" t="n">
-        <v>-12.0918</v>
+        <v>-12.0108</v>
       </c>
       <c r="D5" t="n">
-        <v>-9.393700000000001</v>
+        <v>-9.269299999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6878</v>
+        <v>0.6989</v>
       </c>
       <c r="F5" t="n">
-        <v>-15.6181</v>
+        <v>-15.225</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1232</v>
+        <v>0.1218</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1227</v>
+        <v>0.1213</v>
       </c>
     </row>
     <row r="6">
@@ -608,28 +608,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-10.1396</v>
+        <v>-10.4661</v>
       </c>
       <c r="C6" t="n">
-        <v>-11.499</v>
+        <v>-11.8399</v>
       </c>
       <c r="D6" t="n">
-        <v>-8.780200000000001</v>
+        <v>-9.0923</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6931</v>
+        <v>0.7004</v>
       </c>
       <c r="F6" t="n">
-        <v>-14.6295</v>
+        <v>-14.9426</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1098</v>
+        <v>0.1179</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1092</v>
+        <v>0.1173</v>
       </c>
     </row>
     <row r="7">
@@ -639,28 +639,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.1956</v>
+        <v>1.2751</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.244</v>
+        <v>-0.1863</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6353</v>
+        <v>2.7366</v>
       </c>
       <c r="E7" t="n">
-        <v>0.734</v>
+        <v>0.7451</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6289</v>
+        <v>1.7114</v>
       </c>
       <c r="G7" t="n">
-        <v>0.103512</v>
+        <v>0.087201</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0015</v>
+        <v>0.0017</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="8">
@@ -670,28 +670,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.067500000000001</v>
+        <v>9.0488</v>
       </c>
       <c r="C8" t="n">
-        <v>7.6914</v>
+        <v>7.652</v>
       </c>
       <c r="D8" t="n">
-        <v>10.4435</v>
+        <v>10.4456</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7016</v>
+        <v>0.7121</v>
       </c>
       <c r="F8" t="n">
-        <v>12.924</v>
+        <v>12.7065</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0878</v>
+        <v>0.0881</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0872</v>
+        <v>0.0876</v>
       </c>
     </row>
     <row r="9">
@@ -722,17 +722,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>F=2.868</t>
+          <t>F=2.583</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>6e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>0.048</v>
+        <v>0.0451</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0312</v>
+        <v>0.0276</v>
       </c>
     </row>
   </sheetData>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108.1139</v>
+        <v>109.8381</v>
       </c>
       <c r="C2" t="n">
-        <v>94.1384</v>
+        <v>95.2893</v>
       </c>
       <c r="D2" t="n">
-        <v>122.0895</v>
+        <v>124.3868</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1254</v>
+        <v>7.4175</v>
       </c>
       <c r="F2" t="n">
-        <v>15.173</v>
+        <v>14.808</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -818,19 +818,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42.4144</v>
+        <v>42.6045</v>
       </c>
       <c r="C3" t="n">
-        <v>40.2911</v>
+        <v>40.5318</v>
       </c>
       <c r="D3" t="n">
-        <v>44.5376</v>
+        <v>44.6772</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0825</v>
+        <v>1.0567</v>
       </c>
       <c r="F3" t="n">
-        <v>39.181</v>
+        <v>40.3175</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -843,19 +843,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-6.2976</v>
+        <v>-6.6246</v>
       </c>
       <c r="C4" t="n">
-        <v>-7.2647</v>
+        <v>-7.5751</v>
       </c>
       <c r="D4" t="n">
-        <v>-5.3306</v>
+        <v>-5.6742</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4931</v>
+        <v>0.4846</v>
       </c>
       <c r="F4" t="n">
-        <v>-12.7726</v>
+        <v>-13.6707</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -868,22 +868,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.8698</v>
+        <v>3.9566</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1031</v>
+        <v>-3.562</v>
       </c>
       <c r="D5" t="n">
-        <v>15.6366</v>
+        <v>11.4753</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9599</v>
+        <v>3.8333</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9874</v>
+        <v>1.0322</v>
       </c>
       <c r="G5" t="n">
-        <v>0.047039</v>
+        <v>0.302144</v>
       </c>
     </row>
     <row r="6">
@@ -893,22 +893,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.7723</v>
+        <v>-0.8659</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.5248</v>
+        <v>-2.5758</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.8441</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8935</v>
+        <v>0.8718</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8643</v>
+        <v>-0.9932</v>
       </c>
       <c r="G6" t="n">
-        <v>0.387564</v>
+        <v>0.320754</v>
       </c>
     </row>
     <row r="7">
@@ -918,22 +918,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0441</v>
+        <v>-1.371</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.4361</v>
+        <v>-2.7261</v>
       </c>
       <c r="D7" t="n">
-        <v>1.348</v>
+        <v>-0.0159</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7097</v>
+        <v>0.6909</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0621</v>
+        <v>-1.9844</v>
       </c>
       <c r="G7" t="n">
-        <v>0.950516</v>
+        <v>0.047382</v>
       </c>
     </row>
     <row r="8">
@@ -943,22 +943,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-3.3522</v>
+        <v>-4.8868</v>
       </c>
       <c r="C8" t="n">
-        <v>-4.7897</v>
+        <v>-6.3105</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9147</v>
+        <v>-3.4632</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7329</v>
+        <v>0.7258</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.5738</v>
+        <v>-6.7328</v>
       </c>
       <c r="G8" t="n">
-        <v>5e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.5175</v>
+        <v>5.7831</v>
       </c>
       <c r="C9" t="n">
-        <v>-5.4199</v>
+        <v>-0.9815</v>
       </c>
       <c r="D9" t="n">
-        <v>8.455</v>
+        <v>12.5477</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5371</v>
+        <v>3.4488</v>
       </c>
       <c r="F9" t="n">
-        <v>0.429</v>
+        <v>1.6768</v>
       </c>
       <c r="G9" t="n">
-        <v>0.667947</v>
+        <v>0.093765</v>
       </c>
     </row>
     <row r="10">
@@ -993,22 +993,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.8262</v>
+        <v>0.3467</v>
       </c>
       <c r="C10" t="n">
-        <v>-34.5577</v>
+        <v>-38.0436</v>
       </c>
       <c r="D10" t="n">
-        <v>44.2101</v>
+        <v>38.7369</v>
       </c>
       <c r="E10" t="n">
-        <v>20.0799</v>
+        <v>19.5727</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2403</v>
+        <v>0.0177</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8100889999999999</v>
+        <v>0.985872</v>
       </c>
     </row>
     <row r="11">
@@ -1018,22 +1018,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14.8173</v>
+        <v>13.1192</v>
       </c>
       <c r="C11" t="n">
-        <v>-6.7159</v>
+        <v>-8.323499999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>36.3505</v>
+        <v>34.5619</v>
       </c>
       <c r="E11" t="n">
-        <v>10.9787</v>
+        <v>10.9322</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3496</v>
+        <v>1.2</v>
       </c>
       <c r="G11" t="n">
-        <v>0.177311</v>
+        <v>0.230296</v>
       </c>
     </row>
     <row r="12">
@@ -1043,22 +1043,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19.2802</v>
+        <v>20.6752</v>
       </c>
       <c r="C12" t="n">
-        <v>-20.0604</v>
+        <v>-17.583</v>
       </c>
       <c r="D12" t="n">
-        <v>58.6208</v>
+        <v>58.9334</v>
       </c>
       <c r="E12" t="n">
-        <v>20.0578</v>
+        <v>19.5054</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9612000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="G12" t="n">
-        <v>0.336572</v>
+        <v>0.289313</v>
       </c>
     </row>
     <row r="13">
@@ -1068,22 +1068,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-7.4276</v>
+        <v>-14.2956</v>
       </c>
       <c r="C13" t="n">
-        <v>-47.0764</v>
+        <v>-52.9631</v>
       </c>
       <c r="D13" t="n">
-        <v>32.2213</v>
+        <v>24.372</v>
       </c>
       <c r="E13" t="n">
-        <v>20.215</v>
+        <v>19.7141</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3674</v>
+        <v>-0.7251</v>
       </c>
       <c r="G13" t="n">
-        <v>0.713345</v>
+        <v>0.468468</v>
       </c>
     </row>
     <row r="14">
@@ -1093,22 +1093,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-17.1596</v>
+        <v>-17.9422</v>
       </c>
       <c r="C14" t="n">
-        <v>-37.6925</v>
+        <v>-38.4383</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3733</v>
+        <v>2.5538</v>
       </c>
       <c r="E14" t="n">
-        <v>10.4687</v>
+        <v>10.4496</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6391</v>
+        <v>-1.717</v>
       </c>
       <c r="G14" t="n">
-        <v>0.101371</v>
+        <v>0.086164</v>
       </c>
     </row>
     <row r="15">
@@ -1118,22 +1118,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.6618</v>
+        <v>6.0069</v>
       </c>
       <c r="C15" t="n">
-        <v>-21.8259</v>
+        <v>-22.919</v>
       </c>
       <c r="D15" t="n">
-        <v>37.1496</v>
+        <v>34.9328</v>
       </c>
       <c r="E15" t="n">
-        <v>15.0343</v>
+        <v>14.7475</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.4073</v>
       </c>
       <c r="G15" t="n">
-        <v>0.610381</v>
+        <v>0.683828</v>
       </c>
     </row>
     <row r="16">
@@ -1143,22 +1143,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9.391999999999999</v>
+        <v>6.656</v>
       </c>
       <c r="C16" t="n">
-        <v>-15.989</v>
+        <v>-18.4052</v>
       </c>
       <c r="D16" t="n">
-        <v>34.7731</v>
+        <v>31.7172</v>
       </c>
       <c r="E16" t="n">
-        <v>12.9405</v>
+        <v>12.7771</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7258</v>
+        <v>0.5209</v>
       </c>
       <c r="G16" t="n">
-        <v>0.46807</v>
+        <v>0.602485</v>
       </c>
     </row>
     <row r="17">
@@ -1168,22 +1168,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1176</v>
+        <v>-0.9792999999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>-37.2419</v>
+        <v>-39.3151</v>
       </c>
       <c r="D17" t="n">
-        <v>41.477</v>
+        <v>37.3565</v>
       </c>
       <c r="E17" t="n">
-        <v>20.0674</v>
+        <v>19.545</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1055</v>
+        <v>-0.0501</v>
       </c>
       <c r="G17" t="n">
-        <v>0.915974</v>
+        <v>0.960044</v>
       </c>
     </row>
     <row r="18">
@@ -1193,22 +1193,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21.9471</v>
+        <v>21.9454</v>
       </c>
       <c r="C18" t="n">
-        <v>-3.4965</v>
+        <v>-3.1483</v>
       </c>
       <c r="D18" t="n">
-        <v>47.3907</v>
+        <v>47.0391</v>
       </c>
       <c r="E18" t="n">
-        <v>12.9724</v>
+        <v>12.7937</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6918</v>
+        <v>1.7153</v>
       </c>
       <c r="G18" t="n">
-        <v>0.090863</v>
+        <v>0.086474</v>
       </c>
     </row>
     <row r="19">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-2.6989</v>
+        <v>-3.8755</v>
       </c>
       <c r="C19" t="n">
-        <v>-28.0779</v>
+        <v>-28.9144</v>
       </c>
       <c r="D19" t="n">
-        <v>22.68</v>
+        <v>21.1633</v>
       </c>
       <c r="E19" t="n">
-        <v>12.9395</v>
+        <v>12.7657</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2086</v>
+        <v>-0.3036</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8348</v>
+        <v>0.761478</v>
       </c>
     </row>
     <row r="20">
@@ -1243,22 +1243,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24.5687</v>
+        <v>24.7315</v>
       </c>
       <c r="C20" t="n">
-        <v>2.9112</v>
+        <v>3.19</v>
       </c>
       <c r="D20" t="n">
-        <v>46.2262</v>
+        <v>46.2729</v>
       </c>
       <c r="E20" t="n">
-        <v>11.0421</v>
+        <v>10.9826</v>
       </c>
       <c r="F20" t="n">
-        <v>2.225</v>
+        <v>2.2519</v>
       </c>
       <c r="G20" t="n">
-        <v>0.026212</v>
+        <v>0.024462</v>
       </c>
     </row>
     <row r="21">
@@ -1268,22 +1268,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.6589</v>
+        <v>-0.458</v>
       </c>
       <c r="C21" t="n">
-        <v>-12.4672</v>
+        <v>-15.1197</v>
       </c>
       <c r="D21" t="n">
-        <v>15.785</v>
+        <v>14.2036</v>
       </c>
       <c r="E21" t="n">
-        <v>7.2022</v>
+        <v>7.475</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2303</v>
+        <v>-0.0613</v>
       </c>
       <c r="G21" t="n">
-        <v>0.81786</v>
+        <v>0.951147</v>
       </c>
     </row>
     <row r="22">
@@ -1293,22 +1293,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.7689</v>
+        <v>1.8774</v>
       </c>
       <c r="C22" t="n">
-        <v>-14.82</v>
+        <v>-17.307</v>
       </c>
       <c r="D22" t="n">
-        <v>22.3578</v>
+        <v>21.0618</v>
       </c>
       <c r="E22" t="n">
-        <v>9.477600000000001</v>
+        <v>9.780900000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3977</v>
+        <v>0.1919</v>
       </c>
       <c r="G22" t="n">
-        <v>0.690927</v>
+        <v>0.847808</v>
       </c>
     </row>
     <row r="23">
@@ -1318,22 +1318,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>33.7503</v>
+        <v>34.1999</v>
       </c>
       <c r="C23" t="n">
-        <v>-5.6332</v>
+        <v>-4.1014</v>
       </c>
       <c r="D23" t="n">
-        <v>73.13379999999999</v>
+        <v>72.5012</v>
       </c>
       <c r="E23" t="n">
-        <v>20.0797</v>
+        <v>19.5274</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6808</v>
+        <v>1.7514</v>
       </c>
       <c r="G23" t="n">
-        <v>0.092982</v>
+        <v>0.080067</v>
       </c>
     </row>
     <row r="24">
@@ -1343,22 +1343,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-7.568</v>
+        <v>-9.2258</v>
       </c>
       <c r="C24" t="n">
-        <v>-37.0709</v>
+        <v>-38.1708</v>
       </c>
       <c r="D24" t="n">
-        <v>21.9348</v>
+        <v>19.7193</v>
       </c>
       <c r="E24" t="n">
-        <v>15.042</v>
+        <v>14.7572</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5031</v>
+        <v>-0.6252</v>
       </c>
       <c r="G24" t="n">
-        <v>0.61494</v>
+        <v>0.531946</v>
       </c>
     </row>
     <row r="25">
@@ -1368,22 +1368,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-1.5784</v>
+        <v>-4.5656</v>
       </c>
       <c r="C25" t="n">
-        <v>-15.694</v>
+        <v>-19.2538</v>
       </c>
       <c r="D25" t="n">
-        <v>12.5372</v>
+        <v>10.1226</v>
       </c>
       <c r="E25" t="n">
-        <v>7.1969</v>
+        <v>7.4886</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2193</v>
+        <v>-0.6097</v>
       </c>
       <c r="G25" t="n">
-        <v>0.826429</v>
+        <v>0.5421589999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1393,22 +1393,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-32.3903</v>
+        <v>-32.1274</v>
       </c>
       <c r="C26" t="n">
-        <v>-71.70140000000001</v>
+        <v>-70.3643</v>
       </c>
       <c r="D26" t="n">
-        <v>6.9209</v>
+        <v>6.1095</v>
       </c>
       <c r="E26" t="n">
-        <v>20.0428</v>
+        <v>19.4945</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.6161</v>
+        <v>-1.648</v>
       </c>
       <c r="G26" t="n">
-        <v>0.106269</v>
+        <v>0.099541</v>
       </c>
     </row>
     <row r="27">
@@ -1418,22 +1418,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-21.4713</v>
+        <v>-20.74</v>
       </c>
       <c r="C27" t="n">
-        <v>-51.2355</v>
+        <v>-49.8988</v>
       </c>
       <c r="D27" t="n">
-        <v>8.292899999999999</v>
+        <v>8.418900000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>15.1753</v>
+        <v>14.8662</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.4149</v>
+        <v>-1.3951</v>
       </c>
       <c r="G27" t="n">
-        <v>0.157285</v>
+        <v>0.163173</v>
       </c>
     </row>
     <row r="28">
@@ -1443,22 +1443,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>12.3383</v>
+        <v>12.8929</v>
       </c>
       <c r="C28" t="n">
-        <v>-7.4783</v>
+        <v>-6.9162</v>
       </c>
       <c r="D28" t="n">
-        <v>32.1549</v>
+        <v>32.7019</v>
       </c>
       <c r="E28" t="n">
-        <v>10.1035</v>
+        <v>10.0994</v>
       </c>
       <c r="F28" t="n">
-        <v>1.2212</v>
+        <v>1.2766</v>
       </c>
       <c r="G28" t="n">
-        <v>0.222183</v>
+        <v>0.201925</v>
       </c>
     </row>
     <row r="29">
@@ -1468,22 +1468,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-4.0797</v>
+        <v>-4.6833</v>
       </c>
       <c r="C29" t="n">
-        <v>-18.195</v>
+        <v>-19.3318</v>
       </c>
       <c r="D29" t="n">
-        <v>10.0355</v>
+        <v>9.965199999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>7.1967</v>
+        <v>7.4684</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5669</v>
+        <v>-0.6271</v>
       </c>
       <c r="G29" t="n">
-        <v>0.570861</v>
+        <v>0.53069</v>
       </c>
     </row>
     <row r="30">
@@ -1493,22 +1493,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.8347</v>
+        <v>2.752</v>
       </c>
       <c r="C30" t="n">
-        <v>-16.7218</v>
+        <v>-17.7572</v>
       </c>
       <c r="D30" t="n">
-        <v>24.3912</v>
+        <v>23.2613</v>
       </c>
       <c r="E30" t="n">
-        <v>10.4807</v>
+        <v>10.4564</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3659</v>
+        <v>0.2632</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7145010000000001</v>
+        <v>0.792436</v>
       </c>
     </row>
     <row r="31">
@@ -1518,22 +1518,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4.5895</v>
+        <v>1.4436</v>
       </c>
       <c r="C31" t="n">
-        <v>-11.9734</v>
+        <v>-15.6998</v>
       </c>
       <c r="D31" t="n">
-        <v>21.1523</v>
+        <v>18.5869</v>
       </c>
       <c r="E31" t="n">
-        <v>8.444599999999999</v>
+        <v>8.7403</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5435</v>
+        <v>0.1652</v>
       </c>
       <c r="G31" t="n">
-        <v>0.586871</v>
+        <v>0.868837</v>
       </c>
     </row>
     <row r="32">
@@ -1543,22 +1543,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.9879</v>
+        <v>-2.3188</v>
       </c>
       <c r="C32" t="n">
-        <v>-27.493</v>
+        <v>-27.4995</v>
       </c>
       <c r="D32" t="n">
-        <v>23.5173</v>
+        <v>22.8619</v>
       </c>
       <c r="E32" t="n">
-        <v>13.0038</v>
+        <v>12.838</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1529</v>
+        <v>-0.1806</v>
       </c>
       <c r="G32" t="n">
-        <v>0.878521</v>
+        <v>0.856689</v>
       </c>
     </row>
     <row r="33">
@@ -1568,22 +1568,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4.8128</v>
+        <v>4.7078</v>
       </c>
       <c r="C33" t="n">
-        <v>-24.7046</v>
+        <v>-24.2334</v>
       </c>
       <c r="D33" t="n">
-        <v>34.3301</v>
+        <v>33.6491</v>
       </c>
       <c r="E33" t="n">
-        <v>15.0494</v>
+        <v>14.7553</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3198</v>
+        <v>0.3191</v>
       </c>
       <c r="G33" t="n">
-        <v>0.749162</v>
+        <v>0.749721</v>
       </c>
     </row>
     <row r="34">
@@ -1593,22 +1593,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>9.866400000000001</v>
+        <v>7.9868</v>
       </c>
       <c r="C34" t="n">
-        <v>-29.4612</v>
+        <v>-30.2779</v>
       </c>
       <c r="D34" t="n">
-        <v>49.1939</v>
+        <v>46.2515</v>
       </c>
       <c r="E34" t="n">
-        <v>20.0512</v>
+        <v>19.5087</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4921</v>
+        <v>0.4094</v>
       </c>
       <c r="G34" t="n">
-        <v>0.622741</v>
+        <v>0.682303</v>
       </c>
     </row>
     <row r="35">
@@ -1618,22 +1618,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24.9905</v>
+        <v>24.3266</v>
       </c>
       <c r="C35" t="n">
-        <v>-14.3225</v>
+        <v>-13.925</v>
       </c>
       <c r="D35" t="n">
-        <v>64.3035</v>
+        <v>62.5781</v>
       </c>
       <c r="E35" t="n">
-        <v>20.0437</v>
+        <v>19.502</v>
       </c>
       <c r="F35" t="n">
-        <v>1.2468</v>
+        <v>1.2474</v>
       </c>
       <c r="G35" t="n">
-        <v>0.212643</v>
+        <v>0.212434</v>
       </c>
     </row>
     <row r="36">
@@ -1643,22 +1643,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>43.352</v>
+        <v>43.2313</v>
       </c>
       <c r="C36" t="n">
-        <v>13.8359</v>
+        <v>14.295</v>
       </c>
       <c r="D36" t="n">
-        <v>72.8681</v>
+        <v>72.1675</v>
       </c>
       <c r="E36" t="n">
-        <v>15.0488</v>
+        <v>14.7527</v>
       </c>
       <c r="F36" t="n">
-        <v>2.8808</v>
+        <v>2.9304</v>
       </c>
       <c r="G36" t="n">
-        <v>0.004017</v>
+        <v>0.003432</v>
       </c>
     </row>
     <row r="37">
@@ -1668,22 +1668,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-5.4435</v>
+        <v>-7.2323</v>
       </c>
       <c r="C37" t="n">
-        <v>-19.5389</v>
+        <v>-21.8767</v>
       </c>
       <c r="D37" t="n">
-        <v>8.651999999999999</v>
+        <v>7.412</v>
       </c>
       <c r="E37" t="n">
-        <v>7.1866</v>
+        <v>7.4662</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7574</v>
+        <v>-0.9687</v>
       </c>
       <c r="G37" t="n">
-        <v>0.448885</v>
+        <v>0.332851</v>
       </c>
     </row>
     <row r="38">
@@ -1693,22 +1693,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-44.7209</v>
+        <v>-48.3258</v>
       </c>
       <c r="C38" t="n">
-        <v>-84.1169</v>
+        <v>-86.66630000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>-5.3249</v>
+        <v>-9.9854</v>
       </c>
       <c r="E38" t="n">
-        <v>20.0861</v>
+        <v>19.5473</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.2265</v>
+        <v>-2.4722</v>
       </c>
       <c r="G38" t="n">
-        <v>0.026114</v>
+        <v>0.013528</v>
       </c>
     </row>
     <row r="39">
@@ -1718,22 +1718,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>20.0494</v>
+        <v>19.8802</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3155</v>
+        <v>0.1115</v>
       </c>
       <c r="D39" t="n">
-        <v>39.7833</v>
+        <v>39.6489</v>
       </c>
       <c r="E39" t="n">
-        <v>10.0613</v>
+        <v>10.0788</v>
       </c>
       <c r="F39" t="n">
-        <v>1.9927</v>
+        <v>1.9725</v>
       </c>
       <c r="G39" t="n">
-        <v>0.046452</v>
+        <v>0.048724</v>
       </c>
     </row>
   </sheetData>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1738</v>
+        <v>1673</v>
       </c>
       <c r="C2" t="inlineStr"/>
     </row>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6338</v>
+        <v>0.6579</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6258</v>
+        <v>0.6502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79.52370000000001</v>
+        <v>84.9935</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15154.35</v>
+        <v>14463.11</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15361.85</v>
+        <v>14669.16</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18.521</v>
+        <v>17.8295</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13.2755</v>
+        <v>13.196</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.6299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.065</v>
+        <v>0.0517</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9338</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>107.9121</v>
+        <v>123.4141</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.9803</v>
+        <v>1.9456</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>156.63</v>
+        <v>164.57</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
